--- a/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
@@ -488,46 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, P, I, Plag1</t>
+          <t>t, t_ind_ad, P, I, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9359870862822049</v>
+        <v>0.9512585594899867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01638603015303857</v>
+        <v>0.01667490647703988</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001157831228337022</v>
+        <v>0.001067097361533198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03402691917198825</v>
+        <v>0.03266645621326559</v>
       </c>
       <c r="H2" t="n">
-        <v>254.4133903210768</v>
+        <v>339.4653007346028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02201435597517443</v>
+        <v>0.01786940030607722</v>
       </c>
       <c r="J2" t="n">
-        <v>-1033.225824800526</v>
+        <v>-852.1944459257732</v>
       </c>
       <c r="K2" t="n">
-        <v>-1021.078014390872</v>
+        <v>-838.0130363910158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,32 +535,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, I, Plag1</t>
+          <t>t_ind, P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8739899094178151</v>
+        <v>0.9264360317988727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02233752436155775</v>
+        <v>0.01973990672398544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002279202890292305</v>
+        <v>0.001610537471809194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04774099800268428</v>
+        <v>0.04013150223713528</v>
       </c>
       <c r="H3" t="n">
-        <v>299.8906151920962</v>
+        <v>265.3554353375358</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0408984691978601</v>
+        <v>0.02469656669060463</v>
       </c>
       <c r="J3" t="n">
-        <v>-930.9251440263118</v>
+        <v>-804.3296026065094</v>
       </c>
       <c r="K3" t="n">
-        <v>-921.8142862190709</v>
+        <v>-795.820756885655</v>
       </c>
     </row>
     <row r="4">
@@ -570,36 +570,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>t, P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8667928419773195</v>
+        <v>0.9168242995035651</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02484422633225327</v>
+        <v>0.01908822060761754</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002409379583573131</v>
+        <v>0.001820967325025761</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04908543147995269</v>
+        <v>0.04267279373354597</v>
       </c>
       <c r="H4" t="n">
-        <v>329.0685062603974</v>
+        <v>314.5471988807896</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04414871311530533</v>
+        <v>0.0277273872764485</v>
       </c>
       <c r="J4" t="n">
-        <v>-918.3714438188138</v>
+        <v>-788.8568151494683</v>
       </c>
       <c r="K4" t="n">
-        <v>-903.1866808067456</v>
+        <v>-780.3479694286139</v>
       </c>
     </row>
     <row r="5">
@@ -609,114 +609,114 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>t, P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8647224105035971</v>
+        <v>0.9155635321304998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0249551978752279</v>
+        <v>0.01919319116570673</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002446828436893195</v>
+        <v>0.001848569331105755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04946542668261535</v>
+        <v>0.0429949919305232</v>
       </c>
       <c r="H5" t="n">
-        <v>328.9528363701815</v>
+        <v>321.3803263264102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04479605675474611</v>
+        <v>0.02812493889262409</v>
       </c>
       <c r="J5" t="n">
-        <v>-915.9962417226083</v>
+        <v>-786.9612524744491</v>
       </c>
       <c r="K5" t="n">
-        <v>-900.8114787105401</v>
+        <v>-778.4524067535947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, P, T, I, FS_calc, Plag1, mu_calc</t>
+          <t>t, t_ind_ad, P, I, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8643970193904844</v>
+        <v>0.9149054194765726</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01717541966589703</v>
+        <v>0.01954303643053417</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00245271393671353</v>
+        <v>0.001862977405000354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04952488199595765</v>
+        <v>0.04316222196551463</v>
       </c>
       <c r="H6" t="n">
-        <v>326.2574975244469</v>
+        <v>347.1748091445257</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04589779393855416</v>
+        <v>0.02983245834052848</v>
       </c>
       <c r="J6" t="n">
-        <v>-911.6262612880411</v>
+        <v>-779.9829937811928</v>
       </c>
       <c r="K6" t="n">
-        <v>-890.3675930711456</v>
+        <v>-762.965302339484</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t, P, I, Plag1, mu_calc</t>
+          <t>t, t_ind, t_ind_ad, P, T, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.857890557840848</v>
+        <v>0.9049892477550407</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02520611662987565</v>
+        <v>0.01660948234960077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002570399321280691</v>
+        <v>0.002080072356849035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05069910572466432</v>
+        <v>0.04560781026150056</v>
       </c>
       <c r="H7" t="n">
-        <v>327.41753867824</v>
+        <v>524.0942341915694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04693211217264209</v>
+        <v>0.0369592763232821</v>
       </c>
       <c r="J7" t="n">
-        <v>-908.4088781890605</v>
+        <v>-750.0944274648411</v>
       </c>
       <c r="K7" t="n">
-        <v>-893.2241151769923</v>
+        <v>-710.3864807675204</v>
       </c>
     </row>
     <row r="8">
@@ -726,192 +726,192 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, P, T, I, Plag1, mu_calc</t>
+          <t>t, t_ind, t_ind_ad, P, T, I, Plag1, X_calc, V_calc, mu_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8374674175916947</v>
+        <v>0.860259240562814</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02031837184401247</v>
+        <v>0.02026922376066559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002939802121244204</v>
+        <v>0.00305934732608964</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05421994209923323</v>
+        <v>0.05531136706039402</v>
       </c>
       <c r="H8" t="n">
-        <v>373.4482220283376</v>
+        <v>639.1775973204</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05381763620736253</v>
+        <v>0.05006377095941855</v>
       </c>
       <c r="J8" t="n">
-        <v>-885.7296028617727</v>
+        <v>-705.4837634148225</v>
       </c>
       <c r="K8" t="n">
-        <v>-867.5078872472909</v>
+        <v>-671.4483805314048</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, I, Plag1</t>
+          <t>P, I, Plag1, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8328110020255568</v>
+        <v>0.851538222828903</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02370796591825873</v>
+        <v>0.02144991265131177</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003024024866960126</v>
+        <v>0.003250276747058</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05499113443965423</v>
+        <v>0.057011198435553</v>
       </c>
       <c r="H9" t="n">
-        <v>198.3073714269595</v>
+        <v>472.4629850109692</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05377351679920506</v>
+        <v>0.0493137268742697</v>
       </c>
       <c r="J9" t="n">
-        <v>-887.3796560146244</v>
+        <v>-711.855906798934</v>
       </c>
       <c r="K9" t="n">
-        <v>-878.2687982073835</v>
+        <v>-697.6744972641767</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t, P, I</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7029779595968666</v>
+        <v>0.7805651367073086</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02573424196947342</v>
+        <v>0.02651242503105711</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005372375258517977</v>
+        <v>0.004804091984107939</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07329648871888733</v>
+        <v>0.06931155736316952</v>
       </c>
       <c r="H10" t="n">
-        <v>447.5083708537875</v>
+        <v>878.3558331246738</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09436727480190263</v>
+        <v>0.06969332337668298</v>
       </c>
       <c r="J10" t="n">
-        <v>-798.878712828045</v>
+        <v>-670.6241906710549</v>
       </c>
       <c r="K10" t="n">
-        <v>-789.7678550208041</v>
+        <v>-667.7879087641033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2624991211975743</v>
+        <v>0.7736347719943959</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04801259320762053</v>
+        <v>0.02984775738136616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01333952008758613</v>
+        <v>0.004955818601586399</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1154968401627773</v>
+        <v>0.07039757525360088</v>
       </c>
       <c r="H11" t="n">
-        <v>888.8271824421789</v>
+        <v>1017.313203392419</v>
       </c>
       <c r="I11" t="n">
-        <v>0.231587927702038</v>
+        <v>0.07187864142279173</v>
       </c>
       <c r="J11" t="n">
-        <v>-660.8217290461068</v>
+        <v>-666.7063076255974</v>
       </c>
       <c r="K11" t="n">
-        <v>-654.7478238412796</v>
+        <v>-663.8700257186459</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P, I</t>
+          <t>P, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.195640875434566</v>
+        <v>0.7574804595498456</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04323683912159076</v>
+        <v>0.0332778369965489</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01454881615490017</v>
+        <v>0.005309485296837666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1206184735225088</v>
+        <v>0.0728662150577184</v>
       </c>
       <c r="H12" t="n">
-        <v>913.697368932637</v>
+        <v>1215.667904946883</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2524919086780604</v>
+        <v>0.07797250184283271</v>
       </c>
       <c r="J12" t="n">
-        <v>-647.457830500284</v>
+        <v>-654.0208077971031</v>
       </c>
       <c r="K12" t="n">
-        <v>-641.3839252954567</v>
+        <v>-645.5119620762487</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
@@ -488,163 +488,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, I, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9512585594899867</v>
+        <v>0.8803081255539085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01667490647703988</v>
+        <v>0.01994401755448112</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001067097361533198</v>
+        <v>0.002620416673818821</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03266645621326559</v>
+        <v>0.0511900056047938</v>
       </c>
       <c r="H2" t="n">
-        <v>339.4653007346028</v>
+        <v>666.3650659038062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01786940030607722</v>
+        <v>0.03974185400550064</v>
       </c>
       <c r="J2" t="n">
-        <v>-852.1944459257732</v>
+        <v>-740.9971641937046</v>
       </c>
       <c r="K2" t="n">
-        <v>-838.0130363910158</v>
+        <v>-729.6520365658987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, P, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9264360317988727</v>
+        <v>0.8618052565660718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01973990672398544</v>
+        <v>0.02070355507860628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001610537471809194</v>
+        <v>0.003025500365870533</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04013150223713528</v>
+        <v>0.05500454859255308</v>
       </c>
       <c r="H3" t="n">
-        <v>265.3554353375358</v>
+        <v>707.73857897595</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02469656669060463</v>
+        <v>0.04557627328628786</v>
       </c>
       <c r="J3" t="n">
-        <v>-804.3296026065094</v>
+        <v>-722.8855276625926</v>
       </c>
       <c r="K3" t="n">
-        <v>-795.820756885655</v>
+        <v>-711.5404000347867</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind, t_ind_ad, T, I, FS_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9168242995035651</v>
+        <v>0.7741549659027421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01908822060761754</v>
+        <v>0.0202605742102574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001820967325025761</v>
+        <v>0.004944429985630993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04267279373354597</v>
+        <v>0.07031664088699767</v>
       </c>
       <c r="H4" t="n">
-        <v>314.5471988807896</v>
+        <v>653.5319878693113</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0277273872764485</v>
+        <v>0.07671461121911907</v>
       </c>
       <c r="J4" t="n">
-        <v>-788.8568151494683</v>
+        <v>-646.9961925170103</v>
       </c>
       <c r="K4" t="n">
-        <v>-780.3479694286139</v>
+        <v>-615.797091540544</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9155635321304998</v>
+        <v>0.5328110745689933</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01919319116570673</v>
+        <v>0.03987911193842059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001848569331105755</v>
+        <v>0.0102281767721358</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0429949919305232</v>
+        <v>0.1011344489881455</v>
       </c>
       <c r="H5" t="n">
-        <v>321.3803263264102</v>
+        <v>787.9275933044433</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02812493889262409</v>
+        <v>0.1498164013697971</v>
       </c>
       <c r="J5" t="n">
-        <v>-786.9612524744491</v>
+        <v>-567.4087262566651</v>
       </c>
       <c r="K5" t="n">
-        <v>-778.4524067535947</v>
+        <v>-553.2273167219078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,227 +652,227 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, P, I, Plag1, Xlag1_calc</t>
+          <t>t_ind, t_ind_ad, T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9149054194765726</v>
+        <v>0.4797935120122094</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01954303643053417</v>
+        <v>0.03489003488002618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001862977405000354</v>
+        <v>0.01138889136175986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04316222196551463</v>
+        <v>0.1067187488764737</v>
       </c>
       <c r="H6" t="n">
-        <v>347.1748091445257</v>
+        <v>400.103278250392</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02983245834052848</v>
+        <v>0.1670341703495691</v>
       </c>
       <c r="J6" t="n">
-        <v>-779.9829937811928</v>
+        <v>-551.8647219168328</v>
       </c>
       <c r="K6" t="n">
-        <v>-762.965302339484</v>
+        <v>-534.8470304751239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, P, T, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind, t_ind_ad, T, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9049892477550407</v>
+        <v>0.3625484501274723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01660948234960077</v>
+        <v>0.06390978879846428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002080072356849035</v>
+        <v>0.01395573991774984</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04560781026150056</v>
+        <v>0.1181344146205916</v>
       </c>
       <c r="H7" t="n">
-        <v>524.0942341915694</v>
+        <v>1708.308655480857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0369592763232821</v>
+        <v>0.2035044829041832</v>
       </c>
       <c r="J7" t="n">
-        <v>-750.0944274648411</v>
+        <v>-528.2549133547959</v>
       </c>
       <c r="K7" t="n">
-        <v>-710.3864807675204</v>
+        <v>-514.0735038200386</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, P, T, I, Plag1, X_calc, V_calc, mu_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.860259240562814</v>
+        <v>0.334323587653571</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02026922376066559</v>
+        <v>0.06199967904756401</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00305934732608964</v>
+        <v>0.01457366741353959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05531136706039402</v>
+        <v>0.1207214455411282</v>
       </c>
       <c r="H8" t="n">
-        <v>639.1775973204</v>
+        <v>1571.479211196354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05006377095941855</v>
+        <v>0.2139044908934065</v>
       </c>
       <c r="J8" t="n">
-        <v>-705.4837634148225</v>
+        <v>-516.7959115465651</v>
       </c>
       <c r="K8" t="n">
-        <v>-671.4483805314048</v>
+        <v>-494.1056562909533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, I, Plag1, V_calc, Xlag1_calc</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.851538222828903</v>
+        <v>0.3322180425464248</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02144991265131177</v>
+        <v>0.06147961558642318</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003250276747058</v>
+        <v>0.01461976415596072</v>
       </c>
       <c r="G9" t="n">
-        <v>0.057011198435553</v>
+        <v>0.120912216735782</v>
       </c>
       <c r="H9" t="n">
-        <v>472.4629850109692</v>
+        <v>1586.259514050349</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0493137268742697</v>
+        <v>0.2140684221452451</v>
       </c>
       <c r="J9" t="n">
-        <v>-711.855906798934</v>
+        <v>-518.3980005056256</v>
       </c>
       <c r="K9" t="n">
-        <v>-697.6744972641767</v>
+        <v>-498.5440271569653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7805651367073086</v>
+        <v>0.3287786177336257</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02651242503105711</v>
+        <v>0.06069401929280616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004804091984107939</v>
+        <v>0.01469506355426586</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06931155736316952</v>
+        <v>0.1212231972613569</v>
       </c>
       <c r="H10" t="n">
-        <v>878.3558331246738</v>
+        <v>1467.474544472548</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06969332337668298</v>
+        <v>0.2151529591678984</v>
       </c>
       <c r="J10" t="n">
-        <v>-670.6241906710549</v>
+        <v>-517.750700432994</v>
       </c>
       <c r="K10" t="n">
-        <v>-667.7879087641033</v>
+        <v>-497.8967270843336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t, t_ind, t_ind_ad, T, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7736347719943959</v>
+        <v>0.2181320973457707</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02984775738136616</v>
+        <v>0.03743595288310077</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004955818601586399</v>
+        <v>0.01711745010528404</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07039757525360088</v>
+        <v>0.1308336734380108</v>
       </c>
       <c r="H11" t="n">
-        <v>1017.313203392419</v>
+        <v>1025.926632541542</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07187864142279173</v>
+        <v>0.2500425858699677</v>
       </c>
       <c r="J11" t="n">
-        <v>-666.7063076255974</v>
+        <v>-498.5247645880512</v>
       </c>
       <c r="K11" t="n">
-        <v>-663.8700257186459</v>
+        <v>-478.6707912393908</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P, mu_calc, dXdt_calc</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7574804595498456</v>
+        <v>0.01986041268692684</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0332778369965489</v>
+        <v>0.05534977191774201</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005309485296837666</v>
+        <v>0.02145821618343738</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0728662150577184</v>
+        <v>0.1464862320610281</v>
       </c>
       <c r="H12" t="n">
-        <v>1215.667904946883</v>
+        <v>1978.616395929413</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07797250184283271</v>
+        <v>0.3095626275223282</v>
       </c>
       <c r="J12" t="n">
-        <v>-654.0208077971031</v>
+        <v>-482.0476061798284</v>
       </c>
       <c r="K12" t="n">
-        <v>-645.5119620762487</v>
+        <v>-479.2113242728769</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wrapper/rP_calc/metrics_global.xlsx
@@ -488,118 +488,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc</t>
+          <t>t, t_ind_ad, I, FS_calc, X_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8803081255539085</v>
+        <v>0.7972878895222709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01994401755448112</v>
+        <v>0.02356856175192351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002620416673818821</v>
+        <v>0.004437980412113014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0511900056047938</v>
+        <v>0.06661816878384616</v>
       </c>
       <c r="H2" t="n">
-        <v>666.3650659038062</v>
+        <v>866.1355205336879</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03974185400550064</v>
+        <v>0.06742021943179784</v>
       </c>
       <c r="J2" t="n">
-        <v>-740.9971641937046</v>
+        <v>-668.6120393876403</v>
       </c>
       <c r="K2" t="n">
-        <v>-729.6520365658987</v>
+        <v>-648.7580660389799</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8618052565660718</v>
+        <v>0.7955211896011017</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02070355507860628</v>
+        <v>0.01850420115091022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003025500365870533</v>
+        <v>0.004476658809894738</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05500454859255308</v>
+        <v>0.06690783817980325</v>
       </c>
       <c r="H3" t="n">
-        <v>707.73857897595</v>
+        <v>671.6967400219037</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04557627328628786</v>
+        <v>0.06997730428659581</v>
       </c>
       <c r="J3" t="n">
-        <v>-722.8855276625926</v>
+        <v>-659.5186673329431</v>
       </c>
       <c r="K3" t="n">
-        <v>-711.5404000347867</v>
+        <v>-628.3195663564768</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, I, FS_calc, X_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7741549659027421</v>
+        <v>0.7113037422561344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0202605742102574</v>
+        <v>0.02448765575267982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004944429985630993</v>
+        <v>0.006320433120143395</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07031664088699767</v>
+        <v>0.07950115169067298</v>
       </c>
       <c r="H4" t="n">
-        <v>653.5319878693113</v>
+        <v>843.5433591915597</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07671461121911907</v>
+        <v>0.09353318050726009</v>
       </c>
       <c r="J4" t="n">
-        <v>-646.9961925170103</v>
+        <v>-628.0599102294158</v>
       </c>
       <c r="K4" t="n">
-        <v>-615.797091540544</v>
+        <v>-613.8785006946584</v>
       </c>
     </row>
     <row r="5">
@@ -648,36 +648,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, T, X_calc, V_calc, Xlag1_calc</t>
+          <t>t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4797935120122094</v>
+        <v>0.4367962232402203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03489003488002618</v>
+        <v>0.05768360938183025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01138889136175986</v>
+        <v>0.01233023189091891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1067187488764737</v>
+        <v>0.1110415773074163</v>
       </c>
       <c r="H6" t="n">
-        <v>400.103278250392</v>
+        <v>710.0403207637617</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1670341703495691</v>
+        <v>0.1790922953515772</v>
       </c>
       <c r="J6" t="n">
-        <v>-551.8647219168328</v>
+        <v>-547.858345521602</v>
       </c>
       <c r="K6" t="n">
-        <v>-534.8470304751239</v>
+        <v>-539.3494998007476</v>
       </c>
     </row>
     <row r="7">
@@ -687,153 +687,153 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, T, V_calc, mu_calc</t>
+          <t>t, t_ind_ad, T, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3625484501274723</v>
+        <v>0.3315332190715781</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06390978879846428</v>
+        <v>0.06034929939421788</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01395573991774984</v>
+        <v>0.01463475701040816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1181344146205916</v>
+        <v>0.1209741997717206</v>
       </c>
       <c r="H7" t="n">
-        <v>1708.308655480857</v>
+        <v>1621.95944003832</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2035044829041832</v>
+        <v>0.2127843641858123</v>
       </c>
       <c r="J7" t="n">
-        <v>-528.2549133547959</v>
+        <v>-524.268851249343</v>
       </c>
       <c r="K7" t="n">
-        <v>-514.0735038200386</v>
+        <v>-512.9237236215371</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.334323587653571</v>
+        <v>0.3140042937230375</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06199967904756401</v>
+        <v>0.06167592517039097</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01457366741353959</v>
+        <v>0.01501851813429405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1207214455411282</v>
+        <v>0.1225500637873928</v>
       </c>
       <c r="H8" t="n">
-        <v>1571.479211196354</v>
+        <v>1647.818976901893</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2139044908934065</v>
+        <v>0.2193116745770946</v>
       </c>
       <c r="J8" t="n">
-        <v>-516.7959115465651</v>
+        <v>-517.0073834238117</v>
       </c>
       <c r="K8" t="n">
-        <v>-494.1056562909533</v>
+        <v>-499.9896919821028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3322180425464248</v>
+        <v>0.3113801566873585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06147961558642318</v>
+        <v>0.06129013484138569</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01461976415596072</v>
+        <v>0.01507596842049351</v>
       </c>
       <c r="G9" t="n">
-        <v>0.120912216735782</v>
+        <v>0.1227842352278724</v>
       </c>
       <c r="H9" t="n">
-        <v>1586.259514050349</v>
+        <v>1641.006313013566</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2140684221452451</v>
+        <v>0.2201391308881379</v>
       </c>
       <c r="J9" t="n">
-        <v>-518.3980005056256</v>
+        <v>-516.5263155816157</v>
       </c>
       <c r="K9" t="n">
-        <v>-498.5440271569653</v>
+        <v>-499.5086241399068</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
+          <t>t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3287786177336257</v>
+        <v>0.2715725775715249</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06069401929280616</v>
+        <v>0.0564674246592123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01469506355426586</v>
+        <v>0.01594747657041788</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1212231972613569</v>
+        <v>0.1262833186545946</v>
       </c>
       <c r="H10" t="n">
-        <v>1467.474544472548</v>
+        <v>1366.913597963371</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2151529591678984</v>
+        <v>0.2311914603278351</v>
       </c>
       <c r="J10" t="n">
-        <v>-517.750700432994</v>
+        <v>-515.4452885483736</v>
       </c>
       <c r="K10" t="n">
-        <v>-497.8967270843336</v>
+        <v>-506.9364428275192</v>
       </c>
     </row>
     <row r="11">
@@ -843,36 +843,36 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, V_calc, mu_calc, dXdt_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2181320973457707</v>
+        <v>0.1892702913218689</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03743595288310077</v>
+        <v>0.04064224166254576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01711745010528404</v>
+        <v>0.01774932221933987</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1308336734380108</v>
+        <v>0.1332265822549684</v>
       </c>
       <c r="H11" t="n">
-        <v>1025.926632541542</v>
+        <v>942.6298807843924</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2500425858699677</v>
+        <v>0.2596434381569773</v>
       </c>
       <c r="J11" t="n">
-        <v>-498.5247645880512</v>
+        <v>-491.9574015255774</v>
       </c>
       <c r="K11" t="n">
-        <v>-478.6707912393908</v>
+        <v>-469.2671462699656</v>
       </c>
     </row>
     <row r="12">
